--- a/medical_surveys_questionnaires/050_patient_centered_design_awareness_survey--medical_surveys_questionnaires.xlsx
+++ b/medical_surveys_questionnaires/050_patient_centered_design_awareness_survey--medical_surveys_questionnaires.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -740,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_"patient-centered_design_emphasizes_the_patient's_needs_and_preferences"}</t>
+          <t>patient-centered_design_emphasizes_the_patient's_needs_and_preferences</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': "Patient-centered design emphasizes the patient's needs and preferences"}</t>
+          <t>Patient-centered design emphasizes the patient's needs and preferences</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'patient-centered_design_is_a_design_approach_that_prioritizes_the_needs_of_the_healthcare_organization'}</t>
+          <t>patient-centered_design_is_a_design_approach_that_prioritizes_the_needs_of_the_healthcare_organization</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Patient-centered design is a design approach that prioritizes the needs of the healthcare organization'}</t>
+          <t>Patient-centered design is a design approach that prioritizes the needs of the healthcare organization</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'patient-centered_design_is_the_current_state_of_the_art_in_healthcare'}</t>
+          <t>patient-centered_design_is_the_current_state_of_the_art_in_healthcare</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Patient-centered design is the current state of the art in healthcare'}</t>
+          <t>Patient-centered design is the current state of the art in healthcare</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'patient-centered_approach'}</t>
+          <t>patient-centered_approach</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Patient-centered approach'}</t>
+          <t>Patient-centered approach</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'collaboration_between_patients_and_healthcare_providers'}</t>
+          <t>collaboration_between_patients_and_healthcare_providers</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Collaboration between patients and healthcare providers'}</t>
+          <t>Collaboration between patients and healthcare providers</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'involvement_of_family_members'}</t>
+          <t>involvement_of_family_members</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Involvement of family members'}</t>
+          <t>Involvement of family members</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'use_of_technology'}</t>
+          <t>use_of_technology</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Use of technology'}</t>
+          <t>Use of technology</t>
         </is>
       </c>
     </row>
